--- a/サイト改善ログ.xlsx
+++ b/サイト改善ログ.xlsx
@@ -13,13 +13,17 @@
     <sheet sheetId="7" name="6. 既存レビューのタイムスタンプ修正・整合性チェック" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="7. サイト改善ログのExcel化" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="8. 詳細ページに関連作品セクションを追加" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="9. まとめ記事テンプレート（articlesid.astro" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="10. アリ・アスターまとめ記事データ（articles.js" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="11. まとめ記事一覧ページ作成・詳細ページの導線整備" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="12. まとめ記事へのサイト全体導線を整備" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="122">
   <si>
     <t>日付</t>
   </si>
@@ -75,6 +79,21 @@
     <t>詳細ページに関連作品セクションを追加</t>
   </si>
   <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>まとめ記事テンプレート（articles/[id].astro）新規作成</t>
+  </si>
+  <si>
+    <t>アリ・アスターまとめ記事データ（articles.js）新規作成</t>
+  </si>
+  <si>
+    <t>まとめ記事一覧ページ作成・詳細ページの導線整備</t>
+  </si>
+  <si>
+    <t>まとめ記事へのサイト全体導線を整備</t>
+  </si>
+  <si>
     <t>2026/06　｜　変更の大きさ：大　｜　対象ツール：手動</t>
   </si>
   <si>
@@ -292,6 +311,84 @@
   </si>
   <si>
     <t>スコア0の作品は除外され、関連作品がない場合はセクション自体が非表示になる</t>
+  </si>
+  <si>
+    <t>2026-06-23　｜　変更の大きさ：中　｜　対象ツール：Claude Code</t>
+  </si>
+  <si>
+    <t>src/pages/articles/[id].astro を新規作成。複数作品を横断比較するまとめ記事の動的ルーティングテンプレートを実装。</t>
+  </si>
+  <si>
+    <t>個別レビューページだけでは複数作品の比較ができず、ユーザーが作品選びの判断をしづらかった</t>
+  </si>
+  <si>
+    <t>まとめ記事として複数作品の怖さ指標を一画面で比較できるページが必要だった</t>
+  </si>
+  <si>
+    <t>articles データから動的にページを生成する [id].astro テンプレートを作成</t>
+  </si>
+  <si>
+    <t>各作品ブロック（怖さ指標＋詳細レビューへのリンク）、比較まとめ表、おすすめ順の提案、モトジロウ総評の構成</t>
+  </si>
+  <si>
+    <t>既存のCSS・コンポーネントクラス（seo-summary, work-info-table, timestamp-item, motojiro-casual 等）をそのまま流用し、CSSの追加なしで実装</t>
+  </si>
+  <si>
+    <t>2026-06-23　｜　変更の大きさ：小　｜　対象ツール：Claude Code</t>
+  </si>
+  <si>
+    <t>src/data/articles.js を新規作成。まとめ記事テンプレート（articles/[id].astro）のデータソースとなる記事データファイルを作成。</t>
+  </si>
+  <si>
+    <t>前ステップで作成した articles/[id].astro テンプレートにデータを供給するファイルが必要だった</t>
+  </si>
+  <si>
+    <t>第1弾としてアリ・アスター監督3作品（ヘレディタリー・ミッドサマー・ボーはおそれている）の比較記事を用意</t>
+  </si>
+  <si>
+    <t>articles 配列に記事データ1件（ari-aster-review）を定義</t>
+  </si>
+  <si>
+    <t>filmIds / filmComments / recommendations / モトジロウ総評など、テンプレートが参照する全フィールドを網羅</t>
+  </si>
+  <si>
+    <t>テンプレートとデータが揃い、まとめ記事ページがビルド可能な状態に</t>
+  </si>
+  <si>
+    <t>src/pages/articles/index.astro を新規作成し、まとめ記事の一覧ページを実装。詳細ページのパンくず・戻るボタンも一覧ページへの導線に変更。</t>
+  </si>
+  <si>
+    <t>まとめ記事の詳細ページはあるが一覧ページがなく、記事が増えた際に探しづらかった</t>
+  </si>
+  <si>
+    <t>詳細ページからトップにしか戻れず、まとめ記事間の回遊ができなかった</t>
+  </si>
+  <si>
+    <t>articles/index.astro を新規作成。各記事を作品画像横並び＋タイトル＋抜粋テキストのカード形式で一覧表示</t>
+  </si>
+  <si>
+    <t>既存の page-hero / cards-grid / review-card 構造を流用し、CSSの追加なしで実装</t>
+  </si>
+  <si>
+    <t>詳細ページのパンくず「まとめ記事」をリンク化し、戻るボタンも「← まとめ記事一覧へ戻る」に変更</t>
+  </si>
+  <si>
+    <t>ヘッダーナビ（PC・ドロワー）に「まとめ記事」リンクを追加。トップページに「まとめ記事を読む →」ボタンを追加。一覧カードのPC表示サイズも調整。</t>
+  </si>
+  <si>
+    <t>まとめ記事ページへの導線がなく、URLを直接入力しないとアクセスできなかった</t>
+  </si>
+  <si>
+    <t>一覧カードがPC表示で横幅いっぱいに広がり、レビュー一覧と見た目の統一感がなかった</t>
+  </si>
+  <si>
+    <t>BaseLayout.astro のpc-nav・drawerに「まとめ記事」リンクを追加し、全ページから遷移可能に</t>
+  </si>
+  <si>
+    <t>トップページに「全作品を見る」の下に「まとめ記事を読む →」ボタンを追加</t>
+  </si>
+  <si>
+    <t>一覧カードからwidth:100%を除去し、レビュー一覧と同じレスポンシブ幅（PC時2列→3列）に統一</t>
   </si>
 </sst>
 </file>
@@ -811,7 +908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -916,6 +1013,50 @@
       </c>
       <c r="C9" s="7" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -929,6 +1070,438 @@
     <hyperlink ref="B7" r:id="rId6" location="#'6. 既存レビューのタイムスタンプ修正・整合性チェック'!A1"/>
     <hyperlink ref="B8" r:id="rId7" location="#'7. サイト改善ログのExcel化'!A1"/>
     <hyperlink ref="B9" r:id="rId8" location="#'8. 詳細ページに関連作品セクションを追加'!A1"/>
+    <hyperlink ref="B10" r:id="rId9" location="#'9. まとめ記事テンプレート（articlesid.astro'!A1"/>
+    <hyperlink ref="B11" r:id="rId10" location="#'10. アリ・アスターまとめ記事データ（articles.js'!A1"/>
+    <hyperlink ref="B12" r:id="rId11" location="#'11. まとめ記事一覧ページ作成・詳細ページの導線整備'!A1"/>
+    <hyperlink ref="B13" r:id="rId12" location="#'12. まとめ記事へのサイト全体導線を整備'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="11"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A17" r:id="rId1" location="#'目次'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="11"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A17" r:id="rId1" location="#'目次'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="11"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A17" r:id="rId1" location="#'目次'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="11"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A17" r:id="rId1" location="#'目次'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -952,100 +1525,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -1083,68 +1656,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1182,124 +1755,124 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B23" s="14"/>
     </row>
@@ -1337,92 +1910,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -1460,68 +2033,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1559,92 +2132,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -1682,76 +2255,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1789,84 +2362,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B18" s="14"/>
     </row>

--- a/サイト改善ログ.xlsx
+++ b/サイト改善ログ.xlsx
@@ -17,13 +17,14 @@
     <sheet sheetId="11" name="10. アリ・アスターまとめ記事データ（articles.js" state="visible" r:id="rId14"/>
     <sheet sheetId="12" name="11. まとめ記事一覧ページ作成・詳細ページの導線整備" state="visible" r:id="rId15"/>
     <sheet sheetId="13" name="12. まとめ記事へのサイト全体導線を整備" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="13. タイムスタンプ未取得レビューに準備中メッセージを表示" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="130">
   <si>
     <t>日付</t>
   </si>
@@ -94,6 +95,12 @@
     <t>まとめ記事へのサイト全体導線を整備</t>
   </si>
   <si>
+    <t>2026/06/24</t>
+  </si>
+  <si>
+    <t>タイムスタンプ未取得レビューに準備中メッセージを表示</t>
+  </si>
+  <si>
     <t>2026/06　｜　変更の大きさ：大　｜　対象ツール：手動</t>
   </si>
   <si>
@@ -389,6 +396,24 @@
   </si>
   <si>
     <t>一覧カードからwidth:100%を除去し、レビュー一覧と同じレスポンシブ幅（PC時2列→3列）に統一</t>
+  </si>
+  <si>
+    <t>2026/06/24　｜　変更の大きさ：小　｜　対象ツール：Claude Code</t>
+  </si>
+  <si>
+    <t>タイムスタンプが空配列のレビュー詳細ページで、「この作品のタイムスタンプは準備中です」というメッセージを表示するようにした。</t>
+  </si>
+  <si>
+    <t>タイムスタンプ未取得の作品で攻略ガイドセクションの中身が空のまま表示されていた</t>
+  </si>
+  <si>
+    <t>ユーザーに「情報がない」のか「表示バグ」なのか区別がつかない状態だった</t>
+  </si>
+  <si>
+    <t>[id].astro でtimestamps配列の長さを判定し、空の場合は準備中メッセージを表示</t>
+  </si>
+  <si>
+    <t>破線ボーダーのスタイル（.timestamp-empty）を追加し、準備中であることが視覚的にわかるようにした</t>
   </si>
 </sst>
 </file>
@@ -908,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1056,6 +1081,17 @@
         <v>22</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1074,6 +1110,7 @@
     <hyperlink ref="B11" r:id="rId10" location="#'10. アリ・アスターまとめ記事データ（articles.js'!A1"/>
     <hyperlink ref="B12" r:id="rId11" location="#'11. まとめ記事一覧ページ作成・詳細ページの導線整備'!A1"/>
     <hyperlink ref="B13" r:id="rId12" location="#'12. まとめ記事へのサイト全体導線を整備'!A1"/>
+    <hyperlink ref="B14" r:id="rId13" location="#'13. タイムスタンプ未取得レビューに準備中メッセージを表示'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1097,76 +1134,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1204,76 +1241,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1311,76 +1348,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1418,76 +1455,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1502,6 +1539,105 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A17" r:id="rId1" location="#'目次'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="11"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A16:B16"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A16" r:id="rId1" location="#'目次'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1525,100 +1661,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -1656,68 +1792,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1755,124 +1891,124 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="14"/>
     </row>
@@ -1910,92 +2046,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2033,68 +2169,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2132,92 +2268,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2255,76 +2391,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -2362,84 +2498,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="14"/>
     </row>

--- a/サイト改善ログ.xlsx
+++ b/サイト改善ログ.xlsx
@@ -18,13 +18,14 @@
     <sheet sheetId="12" name="11. まとめ記事一覧ページ作成・詳細ページの導線整備" state="visible" r:id="rId15"/>
     <sheet sheetId="13" name="12. まとめ記事へのサイト全体導線を整備" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="13. タイムスタンプ未取得レビューに準備中メッセージを表示" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="14. SEO対策：titleタグ・meta descript" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="141">
   <si>
     <t>日付</t>
   </si>
@@ -101,6 +102,9 @@
     <t>タイムスタンプ未取得レビューに準備中メッセージを表示</t>
   </si>
   <si>
+    <t>SEO対策：titleタグ・meta description の改善</t>
+  </si>
+  <si>
     <t>2026/06　｜　変更の大きさ：大　｜　対象ツール：手動</t>
   </si>
   <si>
@@ -414,6 +418,36 @@
   </si>
   <si>
     <t>破線ボーダーのスタイル（.timestamp-empty）を追加し、準備中であることが視覚的にわかるようにした</t>
+  </si>
+  <si>
+    <t>2026/06/24　｜　変更の大きさ：中　｜　対象ツール：Claude Code</t>
+  </si>
+  <si>
+    <t>titleタグの区切り文字統一、トップページタイトルへの「ホラー映画」キーワード追加、レビュー一覧ページへのmeta description追加、各レビュー記事のmeta descriptionをレビューデータから動的生成に変更。</t>
+  </si>
+  <si>
+    <t>meta descriptionが全レビュー記事で同一テンプレートだったため、Googleに低品質と判断されやすかった</t>
+  </si>
+  <si>
+    <t>トップページのtitleに「ホラー映画」が含まれず、主要な検索キーワードで引っかかりにくかった</t>
+  </si>
+  <si>
+    <t>レビュー一覧ページにmeta descriptionがなく、検索結果の説明文がGoogleの自動抜粋任せだった</t>
+  </si>
+  <si>
+    <t>区切り文字が半角と全角で不統一だった</t>
+  </si>
+  <si>
+    <t>各レビューのmeta descriptionがタイトル・年・スコア・ジャンル・難易度から自動生成され、全記事でユニークに</t>
+  </si>
+  <si>
+    <t>トップページのtitleを「ビビリ映画部｜ホラー映画の怖さレビュー＆攻略ガイド」に変更</t>
+  </si>
+  <si>
+    <t>レビュー一覧ページにmeta descriptionを追加</t>
+  </si>
+  <si>
+    <t>全ページの区切り文字を全角「｜」に統一</t>
   </si>
 </sst>
 </file>
@@ -933,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1093,6 +1127,17 @@
       </c>
       <c r="C14" s="8" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1111,6 +1156,7 @@
     <hyperlink ref="B12" r:id="rId11" location="#'11. まとめ記事一覧ページ作成・詳細ページの導線整備'!A1"/>
     <hyperlink ref="B13" r:id="rId12" location="#'12. まとめ記事へのサイト全体導線を整備'!A1"/>
     <hyperlink ref="B14" r:id="rId13" location="#'13. タイムスタンプ未取得レビューに準備中メッセージを表示'!A1"/>
+    <hyperlink ref="B15" r:id="rId14" location="#'14. SEO対策：titleタグ・meta descript'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1134,76 +1180,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1241,76 +1287,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1348,76 +1394,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1455,76 +1501,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1562,68 +1608,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1638,6 +1684,137 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A16" r:id="rId1" location="#'目次'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="11"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A20" r:id="rId1" location="#'目次'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1661,100 +1838,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -1792,68 +1969,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1891,124 +2068,124 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" s="14"/>
     </row>
@@ -2046,92 +2223,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2169,68 +2346,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2268,92 +2445,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2391,76 +2568,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -2498,84 +2675,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="14"/>
     </row>

--- a/サイト改善ログ.xlsx
+++ b/サイト改善ログ.xlsx
@@ -19,13 +19,14 @@
     <sheet sheetId="13" name="12. まとめ記事へのサイト全体導線を整備" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="13. タイムスタンプ未取得レビューに準備中メッセージを表示" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="14. SEO対策：titleタグ・meta descript" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="15. トップページにmeta descriptionを追加（" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="149">
   <si>
     <t>日付</t>
   </si>
@@ -105,6 +106,12 @@
     <t>SEO対策：titleタグ・meta description の改善</t>
   </si>
   <si>
+    <t>2026/09/06</t>
+  </si>
+  <si>
+    <t>トップページにmeta descriptionを追加（掲載作品数を動的反映）</t>
+  </si>
+  <si>
     <t>2026/06　｜　変更の大きさ：大　｜　対象ツール：手動</t>
   </si>
   <si>
@@ -448,6 +455,24 @@
   </si>
   <si>
     <t>全ページの区切り文字を全角「｜」に統一</t>
+  </si>
+  <si>
+    <t>2026/09/06　｜　変更の大きさ：小　｜　対象ツール：Claude Code</t>
+  </si>
+  <si>
+    <t>トップページ（index.astro）にmeta descriptionタグを追加。掲載作品数（全○作品）はreviews.lengthから動的に生成する形にした。</t>
+  </si>
+  <si>
+    <t>トップページにmeta descriptionタグ自体が設定されておらず、Googleの検索結果スニペットが本文からの自動抜粋任せになっていた</t>
+  </si>
+  <si>
+    <t>その結果、Google側のキャッシュ更新タイミングによっては検索結果の「全○作品」表記が古いまま表示され続ける状態だった</t>
+  </si>
+  <si>
+    <t>トップページにも他ページ同様のmeta descriptionタグが設定され、掲載作品数が常に最新のreviews.lengthを参照するように</t>
+  </si>
+  <si>
+    <t>検索結果スニペットの反映自体はGoogleの再クロール・キャッシュ更新のタイミング次第のため、即時反映を保証するものではない</t>
   </si>
 </sst>
 </file>
@@ -967,7 +992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1138,6 +1163,17 @@
       </c>
       <c r="C15" s="7" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1157,6 +1193,7 @@
     <hyperlink ref="B13" r:id="rId12" location="#'12. まとめ記事へのサイト全体導線を整備'!A1"/>
     <hyperlink ref="B14" r:id="rId13" location="#'13. タイムスタンプ未取得レビューに準備中メッセージを表示'!A1"/>
     <hyperlink ref="B15" r:id="rId14" location="#'14. SEO対策：titleタグ・meta descript'!A1"/>
+    <hyperlink ref="B16" r:id="rId15" location="#'15. トップページにmeta descriptionを追加（'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1180,76 +1217,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1287,76 +1324,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1394,76 +1431,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1501,76 +1538,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1608,68 +1645,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1707,100 +1744,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="11"/>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -1815,6 +1852,105 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A20" r:id="rId1" location="#'目次'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="11"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A16:B16"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A16" r:id="rId1" location="#'目次'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1838,100 +1974,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -1969,68 +2105,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2068,124 +2204,124 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B23" s="14"/>
     </row>
@@ -2223,92 +2359,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2346,68 +2482,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2445,92 +2581,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2568,76 +2704,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -2675,84 +2811,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" s="14"/>
     </row>
